--- a/XLS/SCRAPE_curiosidades_lote1.xlsx
+++ b/XLS/SCRAPE_curiosidades_lote1.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H39"/>
+  <dimension ref="A1:H31"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -430,13 +430,13 @@
         <v xml:space="preserve">#LoveAffairWithExWife </v>
       </c>
       <c r="B2">
-        <v>8600000</v>
+        <v>9100000</v>
       </c>
       <c r="C2" t="str">
         <v xml:space="preserve">#LoveAffairWithExWife </v>
       </c>
       <c r="D2">
-        <v>45800</v>
+        <v>52900</v>
       </c>
       <c r="E2" t="str">
         <v>loveaffairwithexwife</v>
@@ -445,7 +445,7 @@
         <v>https://www.tiktok.com/@criaturasextranas23/video/7605458055479790879</v>
       </c>
       <c r="G2">
-        <v>175</v>
+        <v>192</v>
       </c>
       <c r="H2" t="str">
         <v>2026-02-11T04:23:55.000Z</v>
@@ -457,7 +457,7 @@
 PO</v>
       </c>
       <c r="B3">
-        <v>4500000</v>
+        <v>5200000</v>
       </c>
       <c r="C3" t="str" xml:space="preserve">
         <v xml:space="preserve">MYSTERIOUS BALL LIGHTNING CAPTURED ON RING DOOR BELL CAMERA: 3/7/2026 3:00 AM
@@ -465,7 +465,7 @@
 #ufo #2026 #scary #fyp #moon </v>
       </c>
       <c r="D3">
-        <v>168400</v>
+        <v>179300</v>
       </c>
       <c r="E3" t="str">
         <v>ufo, 2026, scary, fyp, moon</v>
@@ -474,7 +474,7 @@
         <v>https://www.tiktok.com/@incognitogamingtv/video/7614589296036678942</v>
       </c>
       <c r="G3">
-        <v>5364</v>
+        <v>5729</v>
       </c>
       <c r="H3" t="str">
         <v>2026-03-07T18:55:52.000Z</v>
@@ -485,13 +485,13 @@
         <v/>
       </c>
       <c r="B4">
-        <v>2000000</v>
+        <v>2100000</v>
       </c>
       <c r="C4" t="str">
         <v/>
       </c>
       <c r="D4">
-        <v>93800</v>
+        <v>105500</v>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -500,7 +500,7 @@
         <v>https://www.tiktok.com/@animaiscuriosos34/video/7609354623773609234</v>
       </c>
       <c r="G4">
-        <v>275</v>
+        <v>297</v>
       </c>
       <c r="H4" t="str">
         <v>2026-02-21T16:22:18.000Z</v>
@@ -519,7 +519,7 @@
 #CuriosidadesMilitares #TecnologiaMilitar #ArmasModernas #Engenharia #FatosImpressionantes</v>
       </c>
       <c r="D5">
-        <v>21900</v>
+        <v>22200</v>
       </c>
       <c r="E5" t="str">
         <v>curiosidadesmilitares, tecnologiamilitar, armasmodernas, engenharia, fatosimpressionantes</v>
@@ -528,118 +528,118 @@
         <v>https://www.tiktok.com/@minutox6/video/7594232784156118279</v>
       </c>
       <c r="G5">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H5" t="str">
         <v>2026-01-11T22:21:56.000Z</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v xml:space="preserve">Esse é o MAIOR SER VIVO do planeta 😱#baleia #animals #mar </v>
+    <row r="6" xml:space="preserve">
+      <c r="A6" t="str" xml:space="preserve">
+        <v xml:space="preserve">Numa viajem de cruzeiro aparece uma sereia.
+#sereias </v>
       </c>
       <c r="B6">
         <v>1300000</v>
       </c>
-      <c r="C6" t="str">
-        <v xml:space="preserve">Esse é o MAIOR SER VIVO do planeta 😱#baleia #animals #mar </v>
-      </c>
-      <c r="D6">
-        <v>52900</v>
-      </c>
-      <c r="E6" t="str">
-        <v>baleia, animals, mar</v>
-      </c>
-      <c r="F6" t="str">
-        <v>https://www.tiktok.com/@ocuriiiosotododia/video/7592367892369362184</v>
-      </c>
-      <c r="G6">
-        <v>426</v>
-      </c>
-      <c r="H6" t="str">
-        <v>2026-01-06T21:45:14.000Z</v>
-      </c>
-    </row>
-    <row r="7" xml:space="preserve">
-      <c r="A7" t="str" xml:space="preserve">
+      <c r="C6" t="str" xml:space="preserve">
         <v xml:space="preserve">Numa viajem de cruzeiro aparece uma sereia.
 #sereias </v>
       </c>
+      <c r="D6">
+        <v>41500</v>
+      </c>
+      <c r="E6" t="str">
+        <v>sereias</v>
+      </c>
+      <c r="F6" t="str">
+        <v>https://www.tiktok.com/@melquichagas62/video/7610065652220448021</v>
+      </c>
+      <c r="G6">
+        <v>1059</v>
+      </c>
+      <c r="H6" t="str">
+        <v>2026-02-23T14:21:29.000Z</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v xml:space="preserve">Esse é o MAIOR SER VIVO do planeta 😱#baleia #animals #mar </v>
+      </c>
       <c r="B7">
-        <v>1100000</v>
-      </c>
-      <c r="C7" t="str" xml:space="preserve">
-        <v xml:space="preserve">Numa viajem de cruzeiro aparece uma sereia.
-#sereias </v>
+        <v>1300000</v>
+      </c>
+      <c r="C7" t="str">
+        <v xml:space="preserve">Esse é o MAIOR SER VIVO do planeta 😱#baleia #animals #mar </v>
       </c>
       <c r="D7">
-        <v>36600</v>
+        <v>53700</v>
       </c>
       <c r="E7" t="str">
-        <v>sereias</v>
+        <v>baleia, animals, mar</v>
       </c>
       <c r="F7" t="str">
-        <v>https://www.tiktok.com/@melquichagas62/video/7610065652220448021</v>
+        <v>https://www.tiktok.com/@ocuriiiosotododia/video/7592367892369362184</v>
       </c>
       <c r="G7">
-        <v>983</v>
+        <v>433</v>
       </c>
       <c r="H7" t="str">
-        <v>2026-02-23T14:21:29.000Z</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v xml:space="preserve">#curiosidades #viral #viralvideo #viraltiktok #fatos </v>
+        <v>2026-01-06T21:45:14.000Z</v>
+      </c>
+    </row>
+    <row r="8" xml:space="preserve">
+      <c r="A8" t="str" xml:space="preserve">
+        <v xml:space="preserve">A ORCA treme na base com A CACHALOTE.
+#animais #curiosidades #oceano #orca #incr</v>
       </c>
       <c r="B8">
         <v>1100000</v>
       </c>
-      <c r="C8" t="str">
-        <v xml:space="preserve">#curiosidades #viral #viralvideo #viraltiktok #fatos </v>
-      </c>
-      <c r="D8">
-        <v>18300</v>
-      </c>
-      <c r="E8" t="str">
-        <v>curiosidades, viral, viralvideo, viraltiktok, fatos</v>
-      </c>
-      <c r="F8" t="str">
-        <v>https://www.tiktok.com/@curiosando181/video/7594958355307793671</v>
-      </c>
-      <c r="G8">
-        <v>30</v>
-      </c>
-      <c r="H8" t="str">
-        <v>2026-01-13T21:17:30.000Z</v>
-      </c>
-    </row>
-    <row r="9" xml:space="preserve">
-      <c r="A9" t="str" xml:space="preserve">
-        <v xml:space="preserve">A ORCA treme na base com A CACHALOTE.
-#animais #curiosidades #oceano #orca #incr</v>
-      </c>
-      <c r="B9">
-        <v>1000000</v>
-      </c>
-      <c r="C9" t="str" xml:space="preserve">
+      <c r="C8" t="str" xml:space="preserve">
         <v xml:space="preserve">A ORCA treme na base com A CACHALOTE.
 #animais #curiosidades #oceano #orca #incrivel </v>
       </c>
+      <c r="D8">
+        <v>27700</v>
+      </c>
+      <c r="E8" t="str">
+        <v>animais, curiosidades, oceano, orca, incrivel</v>
+      </c>
+      <c r="F8" t="str">
+        <v>https://www.tiktok.com/@lupinsht/video/7606497013420559624</v>
+      </c>
+      <c r="G8">
+        <v>74</v>
+      </c>
+      <c r="H8" t="str">
+        <v>2026-02-13T23:33:21.000Z</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v xml:space="preserve">#curiosidades #viral #viralvideo #viraltiktok #fatos </v>
+      </c>
+      <c r="B9">
+        <v>1100000</v>
+      </c>
+      <c r="C9" t="str">
+        <v xml:space="preserve">#curiosidades #viral #viralvideo #viraltiktok #fatos </v>
+      </c>
       <c r="D9">
-        <v>24200</v>
+        <v>18500</v>
       </c>
       <c r="E9" t="str">
-        <v>animais, curiosidades, oceano, orca, incrivel</v>
+        <v>curiosidades, viral, viralvideo, viraltiktok, fatos</v>
       </c>
       <c r="F9" t="str">
-        <v>https://www.tiktok.com/@lupinsht/video/7606497013420559624</v>
+        <v>https://www.tiktok.com/@curiosando181/video/7594958355307793671</v>
       </c>
       <c r="G9">
-        <v>72</v>
+        <v>33</v>
       </c>
       <c r="H9" t="str">
-        <v>2026-02-13T23:33:21.000Z</v>
+        <v>2026-01-13T21:17:30.000Z</v>
       </c>
     </row>
     <row r="10">
@@ -647,13 +647,13 @@
         <v>isso a Naza nao conta #humanidades #curiosidades #Ciência #misterio #arqueologia</v>
       </c>
       <c r="B10">
-        <v>870900</v>
+        <v>895900</v>
       </c>
       <c r="C10" t="str">
         <v xml:space="preserve">isso a Naza nao conta #humanidades #curiosidades #Ciência #misterio #arqueologiaprohibida </v>
       </c>
       <c r="D10">
-        <v>21500</v>
+        <v>22400</v>
       </c>
       <c r="E10" t="str">
         <v>humanidades, curiosidades, ciência, misterio, arqueologiaprohibida</v>
@@ -662,146 +662,148 @@
         <v>https://www.tiktok.com/@teoricamente8/video/7600358696299875605</v>
       </c>
       <c r="G10">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="H10" t="str">
         <v>2026-01-28T10:33:36.000Z</v>
       </c>
     </row>
-    <row r="11" xml:space="preserve">
-      <c r="A11" t="str" xml:space="preserve">
+    <row r="11">
+      <c r="A11" t="str">
+        <v>A aposta na cabine de comando que terminou em desastre</v>
+      </c>
+      <c r="B11">
+        <v>817500</v>
+      </c>
+      <c r="C11" t="str">
+        <v>A aposta na cabine de comando que terminou em desastre</v>
+      </c>
+      <c r="D11">
+        <v>15100</v>
+      </c>
+      <c r="E11" t="str">
+        <v/>
+      </c>
+      <c r="F11" t="str">
+        <v>https://www.tiktok.com/@fatoscuriosos762/video/7615033023901224213</v>
+      </c>
+      <c r="G11">
+        <v>92</v>
+      </c>
+      <c r="H11" t="str">
+        <v>2026-03-08T23:37:42.000Z</v>
+      </c>
+    </row>
+    <row r="12" xml:space="preserve">
+      <c r="A12" t="str" xml:space="preserve">
         <v xml:space="preserve">A BOLSA ANUNNAKI!?
 #misterio #curiosidades </v>
       </c>
-      <c r="B11">
-        <v>783800</v>
-      </c>
-      <c r="C11" t="str" xml:space="preserve">
+      <c r="B12">
+        <v>807000</v>
+      </c>
+      <c r="C12" t="str" xml:space="preserve">
         <v xml:space="preserve">A BOLSA ANUNNAKI!?
 #misterio #curiosidades </v>
       </c>
-      <c r="D11">
-        <v>101900</v>
-      </c>
-      <c r="E11" t="str">
+      <c r="D12">
+        <v>104100</v>
+      </c>
+      <c r="E12" t="str">
         <v>misterio, curiosidades</v>
       </c>
-      <c r="F11" t="str">
+      <c r="F12" t="str">
         <v>https://www.tiktok.com/@obra_prima_ofc/video/7613107169487031559</v>
       </c>
-      <c r="G11">
-        <v>1100</v>
-      </c>
-      <c r="H11" t="str">
+      <c r="G12">
+        <v>1123</v>
+      </c>
+      <c r="H12" t="str">
         <v>2026-03-03T19:04:12.000Z</v>
       </c>
     </row>
-    <row r="12" xml:space="preserve">
-      <c r="A12" t="str">
+    <row r="13">
+      <c r="A13" t="str">
+        <v>Como as pessoas dormiam antes das camas existirem? 🛏️ #cama #sono #curiosidades</v>
+      </c>
+      <c r="B13">
+        <v>781600</v>
+      </c>
+      <c r="C13" t="str">
+        <v>Como as pessoas dormiam antes das camas existirem? 🛏️ #cama #sono #curiosidades #biosombria</v>
+      </c>
+      <c r="D13">
+        <v>50200</v>
+      </c>
+      <c r="E13" t="str">
+        <v>cama, sono, curiosidades, biosombria</v>
+      </c>
+      <c r="F13" t="str">
+        <v>https://www.tiktok.com/@biosombria/video/7618362401775258887</v>
+      </c>
+      <c r="G13">
+        <v>140</v>
+      </c>
+      <c r="H13" t="str">
+        <v>2026-03-17T22:57:09.000Z</v>
+      </c>
+    </row>
+    <row r="14" xml:space="preserve">
+      <c r="A14" t="str" xml:space="preserve">
+        <v xml:space="preserve">💀🌴These imposing giants were the rulers of Rapa Nui for centurie.
+#giants #ai </v>
+      </c>
+      <c r="B14">
+        <v>762800</v>
+      </c>
+      <c r="C14" t="str" xml:space="preserve">
+        <v xml:space="preserve">💀🌴These imposing giants were the rulers of Rapa Nui for centurie.
+#giants #ai #island #dangerous #tribe </v>
+      </c>
+      <c r="D14">
+        <v>23300</v>
+      </c>
+      <c r="E14" t="str">
+        <v>giants, ai, island, dangerous, tribe</v>
+      </c>
+      <c r="F14" t="str">
+        <v>https://www.tiktok.com/@swampdiscoveries/video/7617559841845857569</v>
+      </c>
+      <c r="G14">
+        <v>325</v>
+      </c>
+      <c r="H14" t="str">
+        <v>2026-03-15T19:02:46.000Z</v>
+      </c>
+    </row>
+    <row r="15" xml:space="preserve">
+      <c r="A15" t="str">
         <v>Lagos mortais existem no fundo do oceano e parecem cenários de outro planeta. El</v>
       </c>
-      <c r="B12">
-        <v>688600</v>
-      </c>
-      <c r="C12" t="str" xml:space="preserve">
+      <c r="B15">
+        <v>714800</v>
+      </c>
+      <c r="C15" t="str" xml:space="preserve">
         <v xml:space="preserve">Lagos mortais existem no fundo do oceano e parecem cenários de outro planeta. Eles são formados por água extremamente salgada e densa que se acumula em depressões do fundo marinho, criando "poças" separadas da água normal ao redor.
 Lagos mortais recebem esse nome porque a salinidade e a química são tão extremas que muitos animais que entram ali não conseguem sobreviver. A falta de oxigênio e a presença de substâncias tóxicas transformam essas áreas em verdadeiras armadilhas naturais nas profundezas.
 Lagos mortais mostram como o oceano ainda guarda ambientes extremos e pouco conhecidos, onde as regras mudam completamente e só formas de vida altamente adaptadas conseguem existir.
 👉🏻Siga @_mundo_submerso para desvendar os mistérios dos oceanos ⚓ 
 #oceano #curiosidades #mar #fatoscuriosos #fy </v>
       </c>
-      <c r="D12">
-        <v>18800</v>
-      </c>
-      <c r="E12" t="str">
+      <c r="D15">
+        <v>19400</v>
+      </c>
+      <c r="E15" t="str">
         <v>oceano, curiosidades, mar, fatoscuriosos, fy</v>
       </c>
-      <c r="F12" t="str">
+      <c r="F15" t="str">
         <v>https://www.tiktok.com/@_mundo_submerso/video/7606904767813602578</v>
       </c>
-      <c r="G12">
-        <v>161</v>
-      </c>
-      <c r="H12" t="str">
+      <c r="G15">
+        <v>165</v>
+      </c>
+      <c r="H15" t="str">
         <v>2026-02-15T01:55:44.000Z</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>A aposta na cabine de comando que terminou em desastre</v>
-      </c>
-      <c r="B13">
-        <v>671600</v>
-      </c>
-      <c r="C13" t="str">
-        <v>A aposta na cabine de comando que terminou em desastre</v>
-      </c>
-      <c r="D13">
-        <v>12700</v>
-      </c>
-      <c r="E13" t="str">
-        <v/>
-      </c>
-      <c r="F13" t="str">
-        <v>https://www.tiktok.com/@fatoscuriosos762/video/7615033023901224213</v>
-      </c>
-      <c r="G13">
-        <v>70</v>
-      </c>
-      <c r="H13" t="str">
-        <v>2026-03-08T23:37:42.000Z</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>Como as pessoas dormiam antes das camas existirem? 🛏️ #cama #sono #curiosidades</v>
-      </c>
-      <c r="B14">
-        <v>654800</v>
-      </c>
-      <c r="C14" t="str">
-        <v>Como as pessoas dormiam antes das camas existirem? 🛏️ #cama #sono #curiosidades #biosombria</v>
-      </c>
-      <c r="D14">
-        <v>43100</v>
-      </c>
-      <c r="E14" t="str">
-        <v>cama, sono, curiosidades, biosombria</v>
-      </c>
-      <c r="F14" t="str">
-        <v>https://www.tiktok.com/@biosombria/video/7618362401775258887</v>
-      </c>
-      <c r="G14">
-        <v>120</v>
-      </c>
-      <c r="H14" t="str">
-        <v>2026-03-17T22:57:09.000Z</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v xml:space="preserve">#titanic #navio #iceberg #curiosidades </v>
-      </c>
-      <c r="B15">
-        <v>498300</v>
-      </c>
-      <c r="C15" t="str">
-        <v xml:space="preserve">#titanic #navio #iceberg #curiosidades </v>
-      </c>
-      <c r="D15">
-        <v>17200</v>
-      </c>
-      <c r="E15" t="str">
-        <v>titanic, navio, iceberg, curiosidades</v>
-      </c>
-      <c r="F15" t="str">
-        <v>https://www.tiktok.com/@fredcurioso7/video/7589766100536118549</v>
-      </c>
-      <c r="G15">
-        <v>26</v>
-      </c>
-      <c r="H15" t="str">
-        <v>2025-12-30T21:28:56.000Z</v>
       </c>
     </row>
     <row r="16">
@@ -809,13 +811,13 @@
         <v>O gesto simples que salvou camelos no meio do deserto!</v>
       </c>
       <c r="B16">
-        <v>448900</v>
+        <v>683100</v>
       </c>
       <c r="C16" t="str">
         <v>O gesto simples que salvou camelos no meio do deserto!</v>
       </c>
       <c r="D16">
-        <v>10100</v>
+        <v>17900</v>
       </c>
       <c r="E16" t="str">
         <v/>
@@ -824,38 +826,36 @@
         <v>https://www.tiktok.com/@thepeteralves/video/7616008704462195989</v>
       </c>
       <c r="G16">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="H16" t="str">
         <v>2026-03-11T14:43:39.000Z</v>
       </c>
     </row>
-    <row r="17" xml:space="preserve">
-      <c r="A17" t="str" xml:space="preserve">
-        <v xml:space="preserve">💀🌴These imposing giants were the rulers of Rapa Nui for centurie.
-#giants #ai </v>
+    <row r="17">
+      <c r="A17" t="str">
+        <v xml:space="preserve">#titanic #navio #iceberg #curiosidades </v>
       </c>
       <c r="B17">
-        <v>438700</v>
-      </c>
-      <c r="C17" t="str" xml:space="preserve">
-        <v xml:space="preserve">💀🌴These imposing giants were the rulers of Rapa Nui for centurie.
-#giants #ai #island #dangerous #tribe </v>
+        <v>499200</v>
+      </c>
+      <c r="C17" t="str">
+        <v xml:space="preserve">#titanic #navio #iceberg #curiosidades </v>
       </c>
       <c r="D17">
-        <v>12300</v>
+        <v>17200</v>
       </c>
       <c r="E17" t="str">
-        <v>giants, ai, island, dangerous, tribe</v>
+        <v>titanic, navio, iceberg, curiosidades</v>
       </c>
       <c r="F17" t="str">
-        <v>https://www.tiktok.com/@swampdiscoveries/video/7617559841845857569</v>
+        <v>https://www.tiktok.com/@fredcurioso7/video/7589766100536118549</v>
       </c>
       <c r="G17">
-        <v>122</v>
+        <v>26</v>
       </c>
       <c r="H17" t="str">
-        <v>2026-03-15T19:02:46.000Z</v>
+        <v>2025-12-30T21:28:56.000Z</v>
       </c>
     </row>
     <row r="18">
@@ -863,13 +863,13 @@
         <v xml:space="preserve">#filmes #ftv #series #recapdefilmes </v>
       </c>
       <c r="B18">
-        <v>395000</v>
+        <v>422800</v>
       </c>
       <c r="C18" t="str">
         <v xml:space="preserve">#filmes #ftv #series #recapdefilmes </v>
       </c>
       <c r="D18">
-        <v>12700</v>
+        <v>14200</v>
       </c>
       <c r="E18" t="str">
         <v>filmes, ftv, series, recapdefilmes</v>
@@ -878,7 +878,7 @@
         <v>https://www.tiktok.com/@cine_movie_jr/video/7601990308964027669</v>
       </c>
       <c r="G18">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H18" t="str">
         <v>2026-02-01T20:05:05.000Z</v>
@@ -889,13 +889,13 @@
         <v/>
       </c>
       <c r="B19">
-        <v>338400</v>
+        <v>360300</v>
       </c>
       <c r="C19" t="str">
         <v/>
       </c>
       <c r="D19">
-        <v>3455</v>
+        <v>3633</v>
       </c>
       <c r="E19" t="str">
         <v/>
@@ -912,97 +912,13 @@
     </row>
     <row r="20" xml:space="preserve">
       <c r="A20" t="str" xml:space="preserve">
-        <v xml:space="preserve">Bastet Mitologia Egípcia.
-#bastet #mitologiaegipcia #mitologia #egito #egitoanti</v>
-      </c>
-      <c r="B20">
-        <v>201600</v>
-      </c>
-      <c r="C20" t="str" xml:space="preserve">
-        <v xml:space="preserve">Bastet Mitologia Egípcia.
-#bastet #mitologiaegipcia #mitologia #egito #egitoantigo </v>
-      </c>
-      <c r="D20">
-        <v>18900</v>
-      </c>
-      <c r="E20" t="str">
-        <v>bastet, mitologiaegipcia, mitologia, egito, egitoantigo</v>
-      </c>
-      <c r="F20" t="str">
-        <v>https://www.tiktok.com/@mundodasmitologias/video/7599426706931240200</v>
-      </c>
-      <c r="G20">
-        <v>282</v>
-      </c>
-      <c r="H20" t="str">
-        <v>2026-01-25T22:16:57.000Z</v>
-      </c>
-    </row>
-    <row r="21" xml:space="preserve">
-      <c r="A21" t="str" xml:space="preserve">
-        <v xml:space="preserve">lula gigante vs cachalote
-#reinoanimal #vidaselvagem #documentario 
-Descubra a l</v>
-      </c>
-      <c r="B21">
-        <v>178800</v>
-      </c>
-      <c r="C21" t="str" xml:space="preserve">
-        <v xml:space="preserve">lula gigante vs cachalote
-#reinoanimal #vidaselvagem #documentario 
-Descubra a lula gigante e colossal, criaturas reais que inspiraram o mito do Kraken. Explore seu poder e brutalidade em batalhas épicas contra cachalotes e desvende mistérios do oceano profundo</v>
-      </c>
-      <c r="D21">
-        <v>8010</v>
-      </c>
-      <c r="E21" t="str">
-        <v>reinoanimal, vidaselvagem, documentario</v>
-      </c>
-      <c r="F21" t="str">
-        <v>https://www.tiktok.com/@doc_time/video/7615365668401204488</v>
-      </c>
-      <c r="G21">
-        <v>30</v>
-      </c>
-      <c r="H21" t="str">
-        <v>2026-03-09T21:08:18.000Z</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="str">
-        <v>👁️ Você consegue ENCONTRAR CRISTO nessa incrível pintura ? - Procissão de Crist</v>
-      </c>
-      <c r="B22">
-        <v>145200</v>
-      </c>
-      <c r="C22" t="str">
-        <v>👁️ Você consegue ENCONTRAR CRISTO nessa incrível pintura ? - Procissão de Cristo no calvario #jesus#cristo#pintura#quadro#historia#procissao#fe</v>
-      </c>
-      <c r="D22">
-        <v>11200</v>
-      </c>
-      <c r="E22" t="str">
-        <v>jesus, cristo, pintura, quadro, historia, procissao, fe</v>
-      </c>
-      <c r="F22" t="str">
-        <v>https://www.tiktok.com/@sombras_da_historia_/video/7600631751530073364</v>
-      </c>
-      <c r="G22">
-        <v>23</v>
-      </c>
-      <c r="H22" t="str">
-        <v>2026-01-29T12:10:00.000Z</v>
-      </c>
-    </row>
-    <row r="23" xml:space="preserve">
-      <c r="A23" t="str" xml:space="preserve">
         <v xml:space="preserve">Top 10 Dinossauros  Mais Terríveis da Pré-História – Parte 1 😱
 Você acha que o</v>
       </c>
-      <c r="B23">
-        <v>136700</v>
-      </c>
-      <c r="C23" t="str" xml:space="preserve">
+      <c r="B20">
+        <v>291800</v>
+      </c>
+      <c r="C20" t="str" xml:space="preserve">
         <v xml:space="preserve">Top 10 Dinossauros  Mais Terríveis da Pré-História – Parte 1 😱
 Você acha que o T-Rex é o predador mais terrível de todos os tempos? Muitos acham que sim… mas será que ele realmente é o número 1?
 Neste Top 10 Dinossauros Predadores Mais Terríveis revelamos os monstros mais mortais da pré-história com fatos científicos sobre tamanho, dentes, velocidade e estratégias de caça.
@@ -1016,50 +932,132 @@
 Não esquece de curtir, salvar, compartilhar e seguir @extintodoc!
 #dinossauros #top10 #paleontologia #prehistoria #trex #giganotosaurus #carnotaurus #utahraptor #allosaurus #mapusaurus #documentario #animaisextintos #extintodoc</v>
       </c>
+      <c r="D20">
+        <v>10800</v>
+      </c>
+      <c r="E20" t="str">
+        <v>dinossauros, top10, paleontologia, prehistoria, trex, giganotosaurus, carnotaurus, utahraptor, allosaurus, mapusaurus, documentario, animaisextintos, extintodoc</v>
+      </c>
+      <c r="F20" t="str">
+        <v>https://www.tiktok.com/@extintodoc/video/7620806138929499412</v>
+      </c>
+      <c r="G20">
+        <v>184</v>
+      </c>
+      <c r="H20" t="str">
+        <v>2026-03-24T20:05:00.000Z</v>
+      </c>
+    </row>
+    <row r="21" xml:space="preserve">
+      <c r="A21" t="str" xml:space="preserve">
+        <v xml:space="preserve">Bastet Mitologia Egípcia.
+#bastet #mitologiaegipcia #mitologia #egito #egitoanti</v>
+      </c>
+      <c r="B21">
+        <v>203800</v>
+      </c>
+      <c r="C21" t="str" xml:space="preserve">
+        <v xml:space="preserve">Bastet Mitologia Egípcia.
+#bastet #mitologiaegipcia #mitologia #egito #egitoantigo </v>
+      </c>
+      <c r="D21">
+        <v>19200</v>
+      </c>
+      <c r="E21" t="str">
+        <v>bastet, mitologiaegipcia, mitologia, egito, egitoantigo</v>
+      </c>
+      <c r="F21" t="str">
+        <v>https://www.tiktok.com/@mundodasmitologias/video/7599426706931240200</v>
+      </c>
+      <c r="G21">
+        <v>295</v>
+      </c>
+      <c r="H21" t="str">
+        <v>2026-01-25T22:16:57.000Z</v>
+      </c>
+    </row>
+    <row r="22" xml:space="preserve">
+      <c r="A22" t="str" xml:space="preserve">
+        <v xml:space="preserve">lula gigante vs cachalote
+#reinoanimal #vidaselvagem #documentario 
+Descubra a l</v>
+      </c>
+      <c r="B22">
+        <v>194800</v>
+      </c>
+      <c r="C22" t="str" xml:space="preserve">
+        <v xml:space="preserve">lula gigante vs cachalote
+#reinoanimal #vidaselvagem #documentario 
+Descubra a lula gigante e colossal, criaturas reais que inspiraram o mito do Kraken. Explore seu poder e brutalidade em batalhas épicas contra cachalotes e desvende mistérios do oceano profundo</v>
+      </c>
+      <c r="D22">
+        <v>8913</v>
+      </c>
+      <c r="E22" t="str">
+        <v>reinoanimal, vidaselvagem, documentario</v>
+      </c>
+      <c r="F22" t="str">
+        <v>https://www.tiktok.com/@doc_time/video/7615365668401204488</v>
+      </c>
+      <c r="G22">
+        <v>30</v>
+      </c>
+      <c r="H22" t="str">
+        <v>2026-03-09T21:08:18.000Z</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>👁️ Você consegue ENCONTRAR CRISTO nessa incrível pintura ? - Procissão de Crist</v>
+      </c>
+      <c r="B23">
+        <v>152500</v>
+      </c>
+      <c r="C23" t="str">
+        <v>👁️ Você consegue ENCONTRAR CRISTO nessa incrível pintura ? - Procissão de Cristo no calvario #jesus#cristo#pintura#quadro#historia#procissao#fe</v>
+      </c>
       <c r="D23">
-        <v>4945</v>
+        <v>12000</v>
       </c>
       <c r="E23" t="str">
-        <v>dinossauros, top10, paleontologia, prehistoria, trex, giganotosaurus, carnotaurus, utahraptor, allosaurus, mapusaurus, documentario, animaisextintos, extintodoc</v>
+        <v>jesus, cristo, pintura, quadro, historia, procissao, fe</v>
       </c>
       <c r="F23" t="str">
-        <v>https://www.tiktok.com/@extintodoc/video/7620806138929499412</v>
+        <v>https://www.tiktok.com/@sombras_da_historia_/video/7600631751530073364</v>
       </c>
       <c r="G23">
-        <v>109</v>
+        <v>24</v>
       </c>
       <c r="H23" t="str">
-        <v>2026-03-24T20:05:00.000Z</v>
+        <v>2026-01-29T12:10:00.000Z</v>
       </c>
     </row>
     <row r="24" xml:space="preserve">
       <c r="A24" t="str" xml:space="preserve">
-        <v xml:space="preserve">O Gigante do Maranhão: A História do Oxalaia quilombensis 🦖
-Conheça o Oxalaia </v>
+        <v xml:space="preserve">MACHU PICCHU
+#curiosidades #misterio </v>
       </c>
       <c r="B24">
-        <v>134700</v>
+        <v>147600</v>
       </c>
       <c r="C24" t="str" xml:space="preserve">
-        <v xml:space="preserve">O Gigante do Maranhão: A História do Oxalaia quilombensis 🦖
-Conheça o Oxalaia quilombensis, o maior dinossauro carnívoro que já habitou o solo brasileiro. Com 14 metros de comprimento, este titã reinou nos pântanos do Maranhão durante o período Cretáceo. Sua história é marcada pela imponência e pela perda trágica de seus fósseis originais no incêndio do Museu Nacional em 2018. Revisitamos o legado deste imperador da nossa pré-história. 🦖🇧🇷
-Siga o Extinto Doc.
-#Oxalaiaquilombensis #paleontologiaa  #maranhao #dinossauros #prehistoria</v>
+        <v xml:space="preserve">MACHU PICCHU
+#curiosidades #misterio </v>
       </c>
       <c r="D24">
-        <v>6631</v>
+        <v>18100</v>
       </c>
       <c r="E24" t="str">
-        <v>oxalaiaquilombensis, paleontologia, maranhao, dinossauros, prehistoria</v>
+        <v>curiosidades, misterio</v>
       </c>
       <c r="F24" t="str">
-        <v>https://www.tiktok.com/@extintodoc/video/7600508425499364615</v>
+        <v>https://www.tiktok.com/@obra_prima_ofc/video/7622329762387676434</v>
       </c>
       <c r="G24">
-        <v>143</v>
+        <v>193</v>
       </c>
       <c r="H24" t="str">
-        <v>2026-01-28T20:14:33.000Z</v>
+        <v>2026-03-28T15:32:31.000Z</v>
       </c>
     </row>
     <row r="25" xml:space="preserve">
@@ -1068,7 +1066,7 @@
 #reinoanimal #vidaselvagem #docu</v>
       </c>
       <c r="B25">
-        <v>133000</v>
+        <v>144800</v>
       </c>
       <c r="C25" t="str" xml:space="preserve">
         <v xml:space="preserve">tubarão charuto o predador letal e subestimado 
@@ -1076,7 +1074,7 @@
 Descubra o perigoso tubarão charuto, uma ironia da natureza que ataca orcas e coordena ataques complexos. Saiba por que o predador mais eficiente é o que subestimamos, sentindo a parte que falta.</v>
       </c>
       <c r="D25">
-        <v>3369</v>
+        <v>3767</v>
       </c>
       <c r="E25" t="str">
         <v>reinoanimal, vidaselvagem, documentario</v>
@@ -1085,391 +1083,181 @@
         <v>https://www.tiktok.com/@doc_time/video/7611649634351598856</v>
       </c>
       <c r="G25">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="H25" t="str">
         <v>2026-02-27T20:48:12.000Z</v>
       </c>
     </row>
     <row r="26" xml:space="preserve">
-      <c r="A26" t="str" xml:space="preserve">
-        <v xml:space="preserve">GAVIÃO VS VESPAS GIGANTES 
-#wildlife #historia #abelha #gavião</v>
+      <c r="A26" t="str">
+        <v xml:space="preserve">Você sabia que as plataformas de petróleo são algumas das maiores estruturas já </v>
       </c>
       <c r="B26">
-        <v>125500</v>
+        <v>139300</v>
       </c>
       <c r="C26" t="str" xml:space="preserve">
-        <v xml:space="preserve">GAVIÃO VS VESPAS GIGANTES 
-#wildlife #historia #abelha #gavião</v>
-      </c>
-      <c r="D26">
-        <v>4335</v>
-      </c>
-      <c r="E26" t="str">
-        <v>wildlife, historia, abelha, gavião</v>
-      </c>
-      <c r="F26" t="str">
-        <v>https://www.tiktok.com/@largados_/video/7590387234524679444</v>
-      </c>
-      <c r="G26">
-        <v>10</v>
-      </c>
-      <c r="H26" t="str">
-        <v>2026-01-01T16:00:00.000Z</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="str">
-        <v xml:space="preserve">O Dinossauro com MÃOS DE ESPADA! ⚔️🦖 #Therizinossauro #Dinossauros #Fosseis </v>
-      </c>
-      <c r="B27">
-        <v>124300</v>
-      </c>
-      <c r="C27" t="str">
-        <v xml:space="preserve">O Dinossauro com MÃOS DE ESPADA! ⚔️🦖 #Therizinossauro #Dinossauros #Fosseis </v>
-      </c>
-      <c r="D27">
-        <v>2646</v>
-      </c>
-      <c r="E27" t="str">
-        <v>therizinossauro, dinossauros, fosseis</v>
-      </c>
-      <c r="F27" t="str">
-        <v>https://www.tiktok.com/@erasedias/video/7614356830059253000</v>
-      </c>
-      <c r="G27">
-        <v>21</v>
-      </c>
-      <c r="H27" t="str">
-        <v>2026-03-07T13:40:00.000Z</v>
-      </c>
-    </row>
-    <row r="28" xml:space="preserve">
-      <c r="A28" t="str" xml:space="preserve">
-        <v xml:space="preserve">MACHU PICCHU
-#curiosidades #misterio </v>
-      </c>
-      <c r="B28">
-        <v>121000</v>
-      </c>
-      <c r="C28" t="str" xml:space="preserve">
-        <v xml:space="preserve">MACHU PICCHU
-#curiosidades #misterio </v>
-      </c>
-      <c r="D28">
-        <v>15600</v>
-      </c>
-      <c r="E28" t="str">
-        <v>curiosidades, misterio</v>
-      </c>
-      <c r="F28" t="str">
-        <v>https://www.tiktok.com/@obra_prima_ofc/video/7622329762387676434</v>
-      </c>
-      <c r="G28">
-        <v>154</v>
-      </c>
-      <c r="H28" t="str">
-        <v>2026-03-28T15:32:31.000Z</v>
-      </c>
-    </row>
-    <row r="29" xml:space="preserve">
-      <c r="A29" t="str">
-        <v xml:space="preserve">Você sabia que as plataformas de petróleo são algumas das maiores estruturas já </v>
-      </c>
-      <c r="B29">
-        <v>100700</v>
-      </c>
-      <c r="C29" t="str" xml:space="preserve">
         <v xml:space="preserve">Você sabia que as plataformas de petróleo são algumas das maiores estruturas já construídas pelo ser humano? Elas podem parecer simples ilhas metálicas flutuando no meio do oceano, mas na verdade, muitas delas se estendem até o fundo do mar, alcançando profundidades impressionantes.
 Essas plataformas são verdadeiras cidades sobre as águas: possuem dormitórios, refeitórios, laboratórios, guindastes e sistemas complexos de perfuração que atravessam quilômetros de rocha no subsolo marinho. Algumas têm colunas gigantescas de aço e concreto que descem centenas de metros até o leito oceânico, firmando-se como torres submersas de pura engenharia.
 É um espetáculo da força humana diante da imensidão do mar máquinas rugindo, luzes acesas à noite, e o horizonte infinito ao redor. Cada gota de combustível extraída ali vem de uma operação precisa, perigosa e fascinante.
 👉🏻Siga @_mundo_submerso para desvendar os mistérios dos oceanos ⚓ 
 #natureza #oceano #curiosidades #viral #fy </v>
       </c>
+      <c r="D26">
+        <v>4071</v>
+      </c>
+      <c r="E26" t="str">
+        <v>natureza, oceano, curiosidades, viral, fy</v>
+      </c>
+      <c r="F26" t="str">
+        <v>https://www.tiktok.com/@_mundo_submerso/video/7613566546522262791</v>
+      </c>
+      <c r="G26">
+        <v>25</v>
+      </c>
+      <c r="H26" t="str">
+        <v>2026-03-05T00:46:54.000Z</v>
+      </c>
+    </row>
+    <row r="27" xml:space="preserve">
+      <c r="A27" t="str" xml:space="preserve">
+        <v xml:space="preserve">O Gigante do Maranhão: A História do Oxalaia quilombensis 🦖
+Conheça o Oxalaia </v>
+      </c>
+      <c r="B27">
+        <v>137800</v>
+      </c>
+      <c r="C27" t="str" xml:space="preserve">
+        <v xml:space="preserve">O Gigante do Maranhão: A História do Oxalaia quilombensis 🦖
+Conheça o Oxalaia quilombensis, o maior dinossauro carnívoro que já habitou o solo brasileiro. Com 14 metros de comprimento, este titã reinou nos pântanos do Maranhão durante o período Cretáceo. Sua história é marcada pela imponência e pela perda trágica de seus fósseis originais no incêndio do Museu Nacional em 2018. Revisitamos o legado deste imperador da nossa pré-história. 🦖🇧🇷
+Siga o Extinto Doc.
+#Oxalaiaquilombensis #paleontologiaa  #maranhao #dinossauros #prehistoria</v>
+      </c>
+      <c r="D27">
+        <v>6801</v>
+      </c>
+      <c r="E27" t="str">
+        <v>oxalaiaquilombensis, paleontologia, maranhao, dinossauros, prehistoria</v>
+      </c>
+      <c r="F27" t="str">
+        <v>https://www.tiktok.com/@extintodoc/video/7600508425499364615</v>
+      </c>
+      <c r="G27">
+        <v>142</v>
+      </c>
+      <c r="H27" t="str">
+        <v>2026-01-28T20:14:33.000Z</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v xml:space="preserve">O Dinossauro com MÃOS DE ESPADA! ⚔️🦖 #Therizinossauro #Dinossauros #Fosseis </v>
+      </c>
+      <c r="B28">
+        <v>133700</v>
+      </c>
+      <c r="C28" t="str">
+        <v xml:space="preserve">O Dinossauro com MÃOS DE ESPADA! ⚔️🦖 #Therizinossauro #Dinossauros #Fosseis </v>
+      </c>
+      <c r="D28">
+        <v>2874</v>
+      </c>
+      <c r="E28" t="str">
+        <v>therizinossauro, dinossauros, fosseis</v>
+      </c>
+      <c r="F28" t="str">
+        <v>https://www.tiktok.com/@erasedias/video/7614356830059253000</v>
+      </c>
+      <c r="G28">
+        <v>24</v>
+      </c>
+      <c r="H28" t="str">
+        <v>2026-03-07T13:40:00.000Z</v>
+      </c>
+    </row>
+    <row r="29" xml:space="preserve">
+      <c r="A29" t="str" xml:space="preserve">
+        <v xml:space="preserve">GAVIÃO VS VESPAS GIGANTES 
+#wildlife #historia #abelha #gavião</v>
+      </c>
+      <c r="B29">
+        <v>126000</v>
+      </c>
+      <c r="C29" t="str" xml:space="preserve">
+        <v xml:space="preserve">GAVIÃO VS VESPAS GIGANTES 
+#wildlife #historia #abelha #gavião</v>
+      </c>
       <c r="D29">
-        <v>2610</v>
+        <v>4362</v>
       </c>
       <c r="E29" t="str">
-        <v>natureza, oceano, curiosidades, viral, fy</v>
+        <v>wildlife, historia, abelha, gavião</v>
       </c>
       <c r="F29" t="str">
-        <v>https://www.tiktok.com/@_mundo_submerso/video/7613566546522262791</v>
+        <v>https://www.tiktok.com/@largados_/video/7590387234524679444</v>
       </c>
       <c r="G29">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H29" t="str">
-        <v>2026-03-05T00:46:54.000Z</v>
+        <v>2026-01-01T16:00:00.000Z</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v xml:space="preserve">Quando o cacto é invadido #vidaanimal </v>
+        <v>Orca vs Tubarão: Quem é o verdadeiro rei? #animals #viral #fyp #natureza #animai</v>
       </c>
       <c r="B30">
-        <v>99300</v>
+        <v>110800</v>
       </c>
       <c r="C30" t="str">
-        <v xml:space="preserve">Quando o cacto é invadido #vidaanimal </v>
+        <v xml:space="preserve">Orca vs Tubarão: Quem é o verdadeiro rei? #animals #viral #fyp #natureza #animaisnotiktok </v>
       </c>
       <c r="D30">
-        <v>2649</v>
+        <v>2110</v>
       </c>
       <c r="E30" t="str">
-        <v>vidaanimal</v>
+        <v>animals, viral, fyp, natureza, animaisnotiktok</v>
       </c>
       <c r="F30" t="str">
-        <v>https://www.tiktok.com/@naturezasemcena/video/7595652733147925781</v>
+        <v>https://www.tiktok.com/@voz_selvagem/video/7617271614471785736</v>
       </c>
       <c r="G30">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H30" t="str">
-        <v>2026-01-15T18:12:05.000Z</v>
+        <v>2026-03-15T00:24:20.000Z</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Orca vs Tubarão: Quem é o verdadeiro rei? #animals #viral #fyp #natureza #animai</v>
+        <v xml:space="preserve">Quando o cacto é invadido #vidaanimal </v>
       </c>
       <c r="B31">
-        <v>91300</v>
+        <v>100300</v>
       </c>
       <c r="C31" t="str">
-        <v xml:space="preserve">Orca vs Tubarão: Quem é o verdadeiro rei? #animals #viral #fyp #natureza #animaisnotiktok </v>
+        <v xml:space="preserve">Quando o cacto é invadido #vidaanimal </v>
       </c>
       <c r="D31">
-        <v>1581</v>
+        <v>2698</v>
       </c>
       <c r="E31" t="str">
-        <v>animals, viral, fyp, natureza, animaisnotiktok</v>
+        <v>vidaanimal</v>
       </c>
       <c r="F31" t="str">
-        <v>https://www.tiktok.com/@voz_selvagem/video/7617271614471785736</v>
+        <v>https://www.tiktok.com/@naturezasemcena/video/7595652733147925781</v>
       </c>
       <c r="G31">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="H31" t="str">
-        <v>2026-03-15T00:24:20.000Z</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="str">
-        <v xml:space="preserve">O Dinossauro blindado INDESTRUTÍVEL! 🛡️ #Anquilossauro #Fosseis #PreHistoria </v>
-      </c>
-      <c r="B32">
-        <v>72400</v>
-      </c>
-      <c r="C32" t="str">
-        <v xml:space="preserve">O Dinossauro blindado INDESTRUTÍVEL! 🛡️ #Anquilossauro #Fosseis #PreHistoria </v>
-      </c>
-      <c r="D32">
-        <v>1568</v>
-      </c>
-      <c r="E32" t="str">
-        <v>anquilossauro, fosseis, prehistoria</v>
-      </c>
-      <c r="F32" t="str">
-        <v>https://www.tiktok.com/@erasedias/video/7614736236695063815</v>
-      </c>
-      <c r="G32">
-        <v>16</v>
-      </c>
-      <c r="H32" t="str">
-        <v>2026-03-11T20:45:00.000Z</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="str">
-        <v>Esse lugar e inacreditável #humanidades #curiosidades #teorias #Ciência #misteri</v>
-      </c>
-      <c r="B33">
-        <v>70200</v>
-      </c>
-      <c r="C33" t="str">
-        <v xml:space="preserve">Esse lugar e inacreditável #humanidades #curiosidades #teorias #Ciência #misterio </v>
-      </c>
-      <c r="D33">
-        <v>4174</v>
-      </c>
-      <c r="E33" t="str">
-        <v>humanidades, curiosidades, teorias, ciência, misterio</v>
-      </c>
-      <c r="F33" t="str">
-        <v>https://www.tiktok.com/@teoricamente8/video/7600409468530167061</v>
-      </c>
-      <c r="G33">
-        <v>41</v>
-      </c>
-      <c r="H33" t="str">
-        <v>2026-01-28T13:50:34.000Z</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="str">
-        <v/>
-      </c>
-      <c r="B34">
-        <v>61300</v>
-      </c>
-      <c r="C34" t="str">
-        <v/>
-      </c>
-      <c r="D34">
-        <v>5153</v>
-      </c>
-      <c r="E34" t="str">
-        <v/>
-      </c>
-      <c r="F34" t="str">
-        <v>https://www.tiktok.com/@animaiscuriosos34/video/7612010755998764306</v>
-      </c>
-      <c r="G34">
-        <v>15</v>
-      </c>
-      <c r="H34" t="str">
-        <v>2026-02-28T20:09:32.000Z</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="str">
-        <v>Gelo Mortal vs Criaturas Abissais: Quem Domina? #animals #viral #fyp #natureza #</v>
-      </c>
-      <c r="B35">
-        <v>39300</v>
-      </c>
-      <c r="C35" t="str">
-        <v xml:space="preserve">Gelo Mortal vs Criaturas Abissais: Quem Domina? #animals #viral #fyp #natureza #animaisnotiktok </v>
-      </c>
-      <c r="D35">
-        <v>1680</v>
-      </c>
-      <c r="E35" t="str">
-        <v>animals, viral, fyp, natureza, animaisnotiktok</v>
-      </c>
-      <c r="F35" t="str">
-        <v>https://www.tiktok.com/@voz_selvagem/video/7621688239480507655</v>
-      </c>
-      <c r="G35">
-        <v>12</v>
-      </c>
-      <c r="H35" t="str">
-        <v>2026-03-26T22:03:08.000Z</v>
-      </c>
-    </row>
-    <row r="36" xml:space="preserve">
-      <c r="A36" t="str" xml:space="preserve">
-        <v xml:space="preserve">Rising 600 metres above western Tunisia's plains, Jugurtha
-Tableland is a vast 8</v>
-      </c>
-      <c r="B36">
-        <v>37300</v>
-      </c>
-      <c r="C36" t="str" xml:space="preserve">
-        <v xml:space="preserve">Rising 600 metres above western Tunisia's plains, Jugurtha
-Tableland is a vast 80-hectare flat-topped mesa with sheer cliffs and an isolated summit.
-a colossal
-petrified tree stump-once viewed as sacred or cursed, now a striking geological monument. #Jugurthatableland #gianttrees #petrifiedtrees #oldworld #flatearth </v>
-      </c>
-      <c r="D36">
-        <v>1416</v>
-      </c>
-      <c r="E36" t="str">
-        <v>jugurthatableland, gianttrees, petrifiedtrees, oldworld, flatearth</v>
-      </c>
-      <c r="F36" t="str">
-        <v>https://www.tiktok.com/@osireion_abydos/video/7609413124411641118</v>
-      </c>
-      <c r="G36">
-        <v>84</v>
-      </c>
-      <c r="H36" t="str">
-        <v>2026-02-21T20:09:36.000Z</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="str">
-        <v/>
-      </c>
-      <c r="B37">
-        <v>0</v>
-      </c>
-      <c r="C37" t="str">
-        <v/>
-      </c>
-      <c r="D37">
-        <v>0</v>
-      </c>
-      <c r="E37" t="str">
-        <v/>
-      </c>
-      <c r="F37" t="str">
-        <v>https://vt.tiktok.com/ZSHereLKw/</v>
-      </c>
-      <c r="G37" t="str">
-        <v/>
-      </c>
-      <c r="H37" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="str">
-        <v/>
-      </c>
-      <c r="B38">
-        <v>0</v>
-      </c>
-      <c r="C38" t="str">
-        <v/>
-      </c>
-      <c r="D38">
-        <v>0</v>
-      </c>
-      <c r="E38" t="str">
-        <v/>
-      </c>
-      <c r="F38" t="str">
-        <v>https://vt.tiktok.com/ZSH8XhFDX/</v>
-      </c>
-      <c r="G38" t="str">
-        <v/>
-      </c>
-      <c r="H38" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="str">
-        <v/>
-      </c>
-      <c r="B39">
-        <v>0</v>
-      </c>
-      <c r="C39" t="str">
-        <v/>
-      </c>
-      <c r="D39">
-        <v>0</v>
-      </c>
-      <c r="E39" t="str">
-        <v/>
-      </c>
-      <c r="F39" t="str">
-        <v>https://vt.tiktok.com/ZSH84pSP7/</v>
-      </c>
-      <c r="G39" t="str">
-        <v/>
-      </c>
-      <c r="H39" t="str">
-        <v/>
+        <v>2026-01-15T18:12:05.000Z</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H39"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H31"/>
   </ignoredErrors>
 </worksheet>
 </file>